--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rbb13f1568f664c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R989ccf9fab614653"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rb47211045f284e71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rffed339041914c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R9aefc28e848a4f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R94a3ffc268be43dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4e3f7ef9241f430c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Re18dfe1d41f24e4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R15c4419a1b6b40d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R0c83127c60a74e9d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -350,7 +350,7 @@
         <x:v>查看观察窗口对象</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>按对象键全量比较</x:v>
+        <x:v>按对象键核对</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -364,7 +364,7 @@
         <x:v>查看基线窗口对象</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>按对象键全量比较</x:v>
+        <x:v>按对象键核对</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -378,7 +378,7 @@
         <x:v>查看收紧窗口对象</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>按对象键全量比较</x:v>
+        <x:v>按对象键核对</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -397,7 +397,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>工作负载变化</x:v>
+        <x:v>Pod变化记录</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
         <x:v>output/results/workload-changes.csv</x:v>
@@ -411,7 +411,7 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
-        <x:v>保留项</x:v>
+        <x:v>保留项记录</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
         <x:v>output/results/retained-items.csv</x:v>
@@ -431,38 +431,24 @@
         <x:v>output/results/release-summary.json</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>汇总静态结果与现场事项</x:v>
+        <x:v>汇总清单数量与现场操作</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>从明细复算</x:v>
+        <x:v>从阶段与明细复算</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="5" t="str">
-        <x:v>构建入口</x:v>
-      </x:c>
-      <x:c r="B12" s="5" t="str">
-        <x:v>output/tools/build_delivery.py</x:v>
-      </x:c>
-      <x:c r="C12" s="5" t="str">
-        <x:v>从输入重建全部结果</x:v>
-      </x:c>
-      <x:c r="D12" s="5" t="str">
-        <x:v>空目录执行</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="6" t="str">
+      <x:c r="A12" s="6" t="str">
         <x:v>发布说明</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="str">
+      <x:c r="B12" s="6" t="str">
         <x:v>output/RELEASE-NOTES.md</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
-        <x:v>供平台管理员进入维护窗口</x:v>
-      </x:c>
-      <x:c r="D13" s="6" t="str">
-        <x:v>核对责任边界</x:v>
+      <x:c r="C12" s="6" t="str">
+        <x:v>供平台管理员选择维护窗口</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>核对责任与现场操作</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -499,13 +485,13 @@
         <x:v>发布摘要</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>status</x:v>
+        <x:v>package_scope</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>READY</x:v>
+        <x:v>LOCAL_RENDERED_MANIFESTS</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>三套清单构建完成</x:v>
+        <x:v>本地渲染边界</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -513,13 +499,13 @@
         <x:v>发布摘要</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>review_scope</x:v>
+        <x:v>cluster_actions_owner</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>LOCAL_RENDERED_MANIFEST_ONLY</x:v>
+        <x:v>平台管理员</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>本地渲染边界</x:v>
+        <x:v>发布说明</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -575,7 +561,7 @@
         <x:v>RuntimeDefault</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>安全版本清单</x:v>
+        <x:v>后两个阶段的Pod清单</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -679,13 +665,13 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>现场核查</x:v>
+        <x:v>现场操作</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>post_apply_checks</x:v>
+        <x:v>cluster_actions</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>确认Namespace标签已更新、确认准入告警与拒绝来自集群日志、确认目标Pod按发布计划替换</x:v>
+        <x:v>查看Namespace标签、查看目标Pod替换结果、查看集群准入日志</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>集合精确匹配</x:v>
@@ -721,7 +707,7 @@
         <x:v>容差</x:v>
       </x:c>
       <x:c r="E1" s="8" t="str">
-        <x:v>来源与验证</x:v>
+        <x:v>来源与复算方式</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
@@ -735,7 +721,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>无容差</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2" s="5" t="str">
         <x:v>stages.csv数据行数</x:v>
@@ -752,7 +738,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>无容差</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
         <x:v>namespace-labels.csv数据行数</x:v>
@@ -769,7 +755,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>无容差</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
         <x:v>workload-changes.csv数据行数</x:v>
@@ -786,7 +772,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>无容差</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
         <x:v>retained-items.csv数据行数</x:v>
@@ -832,7 +818,7 @@
         <x:v>对象身份、Namespace标签与Pod语义不能变化</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>构建后解析对象</x:v>
+        <x:v>按kind、namespace和name解析</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -860,7 +846,7 @@
         <x:v>表头、复合主键和字段值不能变化</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>按主键排序比较</x:v>
+        <x:v>按复合主键核对</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -871,10 +857,10 @@
         <x:v>键序、缩进和空白可以变化</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>状态、结论边界、数量和现场事项不能变化</x:v>
+        <x:v>材料范围、数量和现场操作不能变化</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>解析JSON比较</x:v>
+        <x:v>解析JSON后核对</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -885,10 +871,10 @@
         <x:v>段落和措辞可以变化</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>本地结论、平台管理员应用和现场核查不能缺失</x:v>
+        <x:v>旧组件负责人、集群责任与本地渲染边界不能缺失</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>定位职责内容</x:v>
+        <x:v>定位责任内容</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R94a3ffc268be43dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4e3f7ef9241f430c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Re18dfe1d41f24e4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R15c4419a1b6b40d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R0c83127c60a74e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rae0ee5103eea4aee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R662a479061b949c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R78786cca78474220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra4b6fc3ef20f4dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra351e409ac4c4b20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -299,13 +299,13 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>观察入口</x:v>
+        <x:v>现行入口</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>output/stages/observe/kustomization.yaml</x:v>
+        <x:v>output/stages/current/kustomization.yaml</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>构建观察窗口清单</x:v>
+        <x:v>保存变更前清单</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>kubectl kustomize</x:v>
@@ -341,13 +341,13 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>观察渲染</x:v>
+        <x:v>现行渲染</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>output/rendered/observe.yaml</x:v>
+        <x:v>output/rendered/current.yaml</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>查看观察窗口对象</x:v>
+        <x:v>查看变更前对象</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>按对象键核对</x:v>
@@ -383,58 +383,58 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>标签记录</x:v>
+        <x:v>阶段计划</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>output/results/namespace-labels.csv</x:v>
+        <x:v>output/results/stage-plan.csv</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>记录阶段Namespace标签</x:v>
+        <x:v>交接窗口、影响、等待、观察和回退</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>按阶段和namespace核对</x:v>
+        <x:v>按stage_id核对</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>Pod变化记录</x:v>
+        <x:v>标签记录</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>output/results/workload-changes.csv</x:v>
+        <x:v>output/results/namespace-labels.csv</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>记录Pod安全字段</x:v>
+        <x:v>记录阶段Namespace标签</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>按阶段和Pod核对</x:v>
+        <x:v>按阶段和namespace核对</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
-        <x:v>保留项记录</x:v>
+        <x:v>Pod变化记录</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>output/results/retained-items.csv</x:v>
+        <x:v>output/results/workload-changes.csv</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>记录旧组件负责人和原因</x:v>
+        <x:v>记录Pod安全字段</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>按category和value核对</x:v>
+        <x:v>按阶段和Pod核对</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
-        <x:v>发布摘要</x:v>
+        <x:v>保留项记录</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>output/results/release-summary.json</x:v>
+        <x:v>output/results/retained-items.csv</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>汇总清单数量与现场操作</x:v>
+        <x:v>记录旧组件负责人和原因</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>从阶段与明细复算</x:v>
+        <x:v>按category和value核对</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -482,41 +482,41 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>发布摘要</x:v>
+        <x:v>current阶段</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>package_scope</x:v>
+        <x:v>window_start_utc</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>LOCAL_RENDERED_MANIFESTS</x:v>
+        <x:v>空</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>本地渲染边界</x:v>
+        <x:v>stages.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>发布摘要</x:v>
+        <x:v>baseline窗口</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>cluster_actions_owner</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="str">
-        <x:v>平台管理员</x:v>
+        <x:v>window_start_utc</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="n">
+        <x:v>46252.083333333336</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>发布说明</x:v>
+        <x:v>stages.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>observe的build-shared</x:v>
+        <x:v>restricted窗口</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>enforce</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="str">
-        <x:v>privileged</x:v>
+        <x:v>window_start_utc</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="n">
+        <x:v>46254.083333333336</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>stages.csv</x:v>
@@ -524,13 +524,13 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>baseline的build-shared</x:v>
+        <x:v>current的build-shared</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
         <x:v>enforce</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>baseline</x:v>
+        <x:v>privileged</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>stages.csv</x:v>
@@ -538,13 +538,13 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>restricted的build-shared</x:v>
+        <x:v>baseline的build-shared</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
         <x:v>enforce</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>restricted</x:v>
+        <x:v>baseline</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>stages.csv</x:v>
@@ -552,29 +552,43 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
+        <x:v>restricted的build-shared</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>enforce</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>restricted</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
+        <x:v>stages.csv</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
         <x:v>安全Pod</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="str">
+      <x:c r="B8" s="5" t="str">
         <x:v>seccomp_type</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str">
+      <x:c r="C8" s="5" t="str">
         <x:v>RuntimeDefault</x:v>
       </x:c>
-      <x:c r="D7" s="5" t="str">
+      <x:c r="D8" s="5" t="str">
         <x:v>后两个阶段的Pod清单</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="6" t="str">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="6" t="str">
         <x:v>安全Pod</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="B9" s="6" t="str">
         <x:v>capabilities_drop</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>ALL</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>容器安全上下文</x:v>
       </x:c>
     </x:row>
@@ -615,7 +629,7 @@
         <x:v>stage_id</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>baseline、observe、restricted</x:v>
+        <x:v>baseline、current、restricted</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>集合精确匹配</x:v>
@@ -664,17 +678,45 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str">
-        <x:v>现场操作</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="str">
-        <x:v>cluster_actions</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="str">
-        <x:v>查看Namespace标签、查看目标Pod替换结果、查看集群准入日志</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="str">
+      <x:c r="A6" s="5" t="str">
+        <x:v>观察信号</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>observation_signals</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>Namespace标签与当前阶段一致、目标Pod在等待预算内完成替换、构建任务没有新增准入拒绝</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="str">
         <x:v>集合精确匹配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>回退条件</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>rollback_triggers</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>Namespace标签与当前阶段不符、目标Pod超过等待预算仍未完成替换、构建流程出现新增准入拒绝</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
+        <x:v>集合精确匹配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>回退目标</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>stage_id和rollback_stage</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>baseline和current、current和current、restricted和baseline</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>复合集合精确匹配</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -712,70 +754,70 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>release-summary.json</x:v>
+        <x:v>stage-plan.csv</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>stage_count</x:v>
-      </x:c>
-      <x:c r="C2" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>baseline的rollout_wait_minutes</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="str">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E2" s="5" t="str">
-        <x:v>stages.csv数据行数</x:v>
+        <x:v>stages.csv对应字段</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>release-summary.json</x:v>
+        <x:v>stage-plan.csv</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>namespace_record_count</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="n">
-        <x:v>12</x:v>
+        <x:v>baseline的observe_minutes</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="str">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="5" t="str">
-        <x:v>namespace-labels.csv数据行数</x:v>
+        <x:v>stages.csv对应字段</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>release-summary.json</x:v>
+        <x:v>stage-plan.csv</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>workload_record_count</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="n">
+        <x:v>restricted的rollout_wait_minutes</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="str">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
-        <x:v>workload-changes.csv数据行数</x:v>
+        <x:v>stages.csv对应字段</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
-        <x:v>release-summary.json</x:v>
+        <x:v>stage-plan.csv</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>retained_item_count</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="n">
-        <x:v>2</x:v>
+        <x:v>restricted的observe_minutes</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>retained-items.csv数据行数</x:v>
+        <x:v>stages.csv对应字段</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -857,7 +899,7 @@
         <x:v>键序、缩进和空白可以变化</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>材料范围、数量和现场操作不能变化</x:v>
+        <x:v>保留项、观察信号和回退条件不能变化</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>解析JSON后核对</x:v>
@@ -871,10 +913,10 @@
         <x:v>段落和措辞可以变化</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>旧组件负责人、集群责任与本地渲染边界不能缺失</x:v>
+        <x:v>旧组件负责人、分批推进、影响范围、等待预算、观察时间与回退安排不能缺失</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>定位责任内容</x:v>
+        <x:v>定位窗口与责任内容</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rae0ee5103eea4aee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R662a479061b949c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R78786cca78474220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra4b6fc3ef20f4dcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra351e409ac4c4b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R21d3ab13a36f415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rb5990dcba27f4b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Ra3689399509d47f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R4c902a05e1a64c39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rab7df3cfd1354aec"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R21d3ab13a36f415d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rb5990dcba27f4b34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Ra3689399509d47f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R4c902a05e1a64c39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rab7df3cfd1354aec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Re1a4586c5aea48c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R9d30243e528f4f59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R7f6adaa542fd4378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rc9b0808878e94ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R3571c1b510d64c15"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -501,8 +501,8 @@
       <x:c r="B3" s="5" t="str">
         <x:v>window_start_utc</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="n">
-        <x:v>46252.083333333336</x:v>
+      <x:c r="C3" s="5" t="str">
+        <x:v>2026年8月18日02:00UTC</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>stages.csv</x:v>
@@ -515,8 +515,8 @@
       <x:c r="B4" s="5" t="str">
         <x:v>window_start_utc</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="n">
-        <x:v>46254.083333333336</x:v>
+      <x:c r="C4" s="5" t="str">
+        <x:v>2026年8月20日02:00UTC</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>stages.csv</x:v>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Re1a4586c5aea48c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R9d30243e528f4f59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R7f6adaa542fd4378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rc9b0808878e94ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R3571c1b510d64c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R912c7b400a0d4451"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R92a736f20e684e61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R8bb2708073614a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rd0511d48a8f44f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc5a56f9f4c6647c1"/>
   </x:sheets>
 </x:workbook>
 </file>
